--- a/Esami_date.xlsx
+++ b/Esami_date.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sabri\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sabri\Desktop\Informatica_Uni\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C317738B-759A-4E84-AAAE-35CECF739B7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8072C382-5CD7-44D8-A299-3575B9FDFA68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{99BD12D4-B8E6-49E2-9F85-BAFC211A9808}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>Maggio</t>
   </si>
@@ -102,6 +102,9 @@
   </si>
   <si>
     <t>8 (o 11)</t>
+  </si>
+  <si>
+    <t>Dicembre</t>
   </si>
 </sst>
 </file>
@@ -608,17 +611,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94AE4C6B-F76A-4BEF-A18E-BA8397C94220}">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultRowHeight="27.6" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.33203125" style="4" customWidth="1"/>
-    <col min="2" max="7" width="9.44140625" style="4" customWidth="1"/>
-    <col min="8" max="8" width="10.44140625" style="4" customWidth="1"/>
+    <col min="2" max="8" width="9.44140625" style="4" customWidth="1"/>
     <col min="9" max="9" width="8.88671875" style="4" customWidth="1"/>
     <col min="10" max="16384" width="8.88671875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -638,8 +640,11 @@
       <c r="G1" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H1" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
@@ -657,8 +662,9 @@
       <c r="G2" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H2" s="7"/>
+    </row>
+    <row r="3" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>7</v>
       </c>
@@ -678,8 +684,9 @@
         <v>22</v>
       </c>
       <c r="G3" s="10"/>
-    </row>
-    <row r="4" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H3" s="10"/>
+    </row>
+    <row r="4" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>10</v>
       </c>
@@ -693,10 +700,17 @@
       <c r="E4" s="9">
         <v>16</v>
       </c>
-      <c r="F4" s="9"/>
-      <c r="G4" s="10"/>
-    </row>
-    <row r="5" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F4" s="9">
+        <v>22</v>
+      </c>
+      <c r="G4" s="10">
+        <v>12</v>
+      </c>
+      <c r="H4" s="10">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>11</v>
       </c>
@@ -714,8 +728,9 @@
         <v>20</v>
       </c>
       <c r="G5" s="10"/>
-    </row>
-    <row r="6" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H5" s="10"/>
+    </row>
+    <row r="6" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>9</v>
       </c>
@@ -733,8 +748,9 @@
       <c r="G6" s="10">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H6" s="10"/>
+    </row>
+    <row r="7" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>8</v>
       </c>
@@ -754,8 +770,9 @@
       <c r="G7" s="7">
         <v>11</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H7" s="7"/>
+    </row>
+    <row r="8" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
         <v>12</v>
       </c>
@@ -773,8 +790,9 @@
         <v>20</v>
       </c>
       <c r="G8" s="10"/>
-    </row>
-    <row r="9" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H8" s="10"/>
+    </row>
+    <row r="9" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>13</v>
       </c>
@@ -784,8 +802,9 @@
       <c r="E9" s="6"/>
       <c r="F9" s="6"/>
       <c r="G9" s="7"/>
-    </row>
-    <row r="10" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H9" s="7"/>
+    </row>
+    <row r="10" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>14</v>
       </c>
@@ -807,8 +826,9 @@
       <c r="G10" s="10">
         <v>12</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H10" s="10"/>
+    </row>
+    <row r="11" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>15</v>
       </c>
@@ -824,8 +844,9 @@
       </c>
       <c r="F11" s="6"/>
       <c r="G11" s="7"/>
-    </row>
-    <row r="12" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H11" s="7"/>
+    </row>
+    <row r="12" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
         <v>16</v>
       </c>
@@ -845,8 +866,9 @@
       <c r="G12" s="10">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H12" s="10"/>
+    </row>
+    <row r="13" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>17</v>
       </c>
@@ -866,8 +888,9 @@
       <c r="G13" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H13" s="7"/>
+    </row>
+    <row r="14" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>18</v>
       </c>
@@ -885,8 +908,9 @@
         <v>27</v>
       </c>
       <c r="G14" s="7"/>
-    </row>
-    <row r="15" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H14" s="7"/>
+    </row>
+    <row r="15" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>19</v>
       </c>
@@ -904,8 +928,9 @@
       <c r="G15" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H15" s="7"/>
+    </row>
+    <row r="16" spans="1:8" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>20</v>
       </c>
@@ -925,6 +950,7 @@
       <c r="G16" s="7">
         <v>10</v>
       </c>
+      <c r="H16" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
